--- a/docs/package/05_Delivery/Upload_Templates/Branch_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Branch_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="120" uniqueCount="72">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="74">
   <si>
     <t xml:space="preserve">Branch Code</t>
   </si>
@@ -39,108 +39,114 @@
     <t xml:space="preserve">Address Line 3</t>
   </si>
   <si>
+    <t xml:space="preserve">City / Municipality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Province</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Country</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Phone Number</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fax</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Status</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ILO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iloilo Branch</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iorta TechNXT Corp.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iloilo@bayanihanbrokers.example.ph</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Western Visayas sales office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit 305, Atria Park District</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mandurriao</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iloilo City</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Iloilo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Philippines</t>
+  </si>
+  <si>
+    <t xml:space="preserve">+63 33 321 4455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Column</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Required</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Format</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allowed values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Example</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Other accepted headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Text</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BranchCode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BranchName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CompanyName</t>
+  </si>
+  <si>
+    <t xml:space="preserve">E-mail address</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EmailID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AddressLine1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AddressLine2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AddressLine3</t>
+  </si>
+  <si>
     <t xml:space="preserve">City</t>
   </si>
   <si>
     <t xml:space="preserve">State</t>
   </si>
   <si>
-    <t xml:space="preserve">Country</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Phone Number</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fax</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ILO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iloilo Branch</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iorta TechNXT Corp.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iloilo@bayanihanbrokers.example.ph</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Western Visayas sales office</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Unit 305, Atria Park District</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mandurriao</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iloilo City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Iloilo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Philippines</t>
-  </si>
-  <si>
-    <t xml:space="preserve">+63 33 321 4455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Column</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Required</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Format</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Allowed values</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Example</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other accepted headers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Text</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BranchCode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BranchName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CompanyName</t>
-  </si>
-  <si>
-    <t xml:space="preserve">E-mail address</t>
-  </si>
-  <si>
-    <t xml:space="preserve">EmailID</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddressLine1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddressLine2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AddressLine3</t>
-  </si>
-  <si>
     <t xml:space="preserve">PhoneNumber</t>
   </si>
   <si>
@@ -192,7 +198,7 @@
     <t xml:space="preserve">Required columns</t>
   </si>
   <si>
-    <t xml:space="preserve">Branch Code, Branch Name, Company Name, Email ID, City, State, Country (dark red headers on the Data sheet). Other columns may be left empty or removed.</t>
+    <t xml:space="preserve">Branch Code, Branch Name, Company Name, Email ID, City / Municipality, Province, Country (dark red headers on the Data sheet). Other columns may be left empty or removed.</t>
   </si>
   <si>
     <t xml:space="preserve">Header row</t>
@@ -368,7 +374,7 @@
     <col min="6" max="6" width="20" customWidth="1"/>
     <col min="7" max="7" width="20" customWidth="1"/>
     <col min="8" max="8" width="20" customWidth="1"/>
-    <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="9" max="9" width="25" customWidth="1"/>
     <col min="10" max="10" width="14" customWidth="1"/>
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
@@ -636,6 +642,9 @@
       <c r="E10" s="0" t="s">
         <v>21</v>
       </c>
+      <c r="F10" s="4" t="s">
+        <v>42</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
@@ -650,6 +659,9 @@
       <c r="E11" s="0" t="s">
         <v>22</v>
       </c>
+      <c r="F11" s="4" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
@@ -679,7 +691,7 @@
         <v>24</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14">
@@ -701,13 +713,13 @@
         <v>38</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -726,106 +738,106 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="0" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/docs/package/05_Delivery/Upload_Templates/Branch_Upload_Template.xlsx
+++ b/docs/package/05_Delivery/Upload_Templates/Branch_Upload_Template.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="135" uniqueCount="80">
   <si>
     <t xml:space="preserve">Branch Code</t>
   </si>
@@ -54,6 +54,15 @@
     <t xml:space="preserve">Fax</t>
   </si>
   <si>
+    <t xml:space="preserve">Issuing Office</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Region</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Numbering Code</t>
+  </si>
+  <si>
     <t xml:space="preserve">Status</t>
   </si>
   <si>
@@ -150,6 +159,21 @@
     <t xml:space="preserve">PhoneNumber</t>
   </si>
   <si>
+    <t xml:space="preserve">Yes or No</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IssuingOffice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">One of the allowed values</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NCR, CAR, Region I, Region II, Region III, Region IV-A, MIMAROPA, Region V, Region VI, Region VII, Region VIII, Region IX, Region X, Region XI, Region XII, Region XIII, BARMM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NumberingCode</t>
+  </si>
+  <si>
     <t xml:space="preserve">Active when empty</t>
   </si>
   <si>
@@ -177,12 +201,6 @@
     <t xml:space="preserve">Master &gt; Generals &gt; Organization &gt; Branch (no Upload button on this screen yet: a System Administrator uploads the file through the API route)</t>
   </si>
   <si>
-    <t xml:space="preserve">API route</t>
-  </si>
-  <si>
-    <t xml:space="preserve">POST /api/masters/branch/upload (multipart field "file")</t>
-  </si>
-  <si>
     <t xml:space="preserve">File types</t>
   </si>
   <si>
@@ -213,10 +231,10 @@
     <t xml:space="preserve">The rows under the header on the Data sheet are samples. Delete them before you upload your own data.</t>
   </si>
   <si>
-    <t xml:space="preserve">Dates and amounts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Enter dates as YYYY-MM-DD and amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
+    <t xml:space="preserve">Amounts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter amounts as plain numbers (no peso sign, no thousands separator). The Data sheet cells are formatted as text so that Excel keeps what you type.</t>
   </si>
   <si>
     <t xml:space="preserve">What happens on errors</t>
@@ -231,10 +249,10 @@
     <t xml:space="preserve">Each row creates a new record, checked exactly like Add on the screen. A row whose code already exists is refused (edit existing records on the screen).</t>
   </si>
   <si>
-    <t xml:space="preserve">Source</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Generated by backend/scripts/build-upload-templates.js from the column list the importer itself uses. Do not rename the headers.</t>
+    <t xml:space="preserve">Headers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">The headers are the ones the import reads. Do not rename them.</t>
   </si>
 </sst>
 </file>
@@ -242,9 +260,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="164" formatCode="dd/mm/yyyy"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
@@ -271,8 +289,42 @@
       <name val="Calibri"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FF0B2A4A"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF5F6B76"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -300,6 +352,24 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFF4CC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -331,9 +401,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -354,6 +424,13 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -363,7 +440,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N2"/>
+  <dimension ref="A1:Q2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
@@ -379,10 +456,13 @@
     <col min="11" max="11" width="14" customWidth="1"/>
     <col min="12" max="12" width="18" customWidth="1"/>
     <col min="13" max="13" width="14" customWidth="1"/>
-    <col min="14" max="14" width="14" customWidth="1"/>
+    <col min="14" max="14" width="20" customWidth="1"/>
+    <col min="15" max="15" width="14" customWidth="1"/>
+    <col min="16" max="16" width="20" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="20" customHeight="1">
+    <row r="1" spans="1:17" ht="20" customHeight="1">
       <c r="A1" s="7" t="s">
         <v>0</v>
       </c>
@@ -425,40 +505,49 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="C2" s="0" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="D2" s="0" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="G2" s="0" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="I2" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="K2" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="L2" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -468,7 +557,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F18"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="28" customWidth="1"/>
@@ -481,22 +570,22 @@
   <sheetData>
     <row r="1" spans="1:6" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="2">
@@ -504,16 +593,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E2" s="0" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3">
@@ -521,16 +610,16 @@
         <v>1</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E3" s="0" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
@@ -538,16 +627,16 @@
         <v>2</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E4" s="0" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5">
@@ -555,16 +644,16 @@
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="E5" s="0" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6">
@@ -572,13 +661,13 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E6" s="0" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -586,16 +675,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E7" s="0" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8">
@@ -603,16 +692,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E8" s="0" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9">
@@ -620,13 +709,13 @@
         <v>7</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="F9" s="4" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10">
@@ -634,16 +723,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E10" s="0" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11">
@@ -651,16 +740,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E11" s="0" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12">
@@ -668,13 +757,13 @@
         <v>10</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E12" s="0" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
     </row>
     <row r="13">
@@ -682,16 +771,16 @@
         <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E13" s="0" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
@@ -699,10 +788,10 @@
         <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
     </row>
     <row r="15">
@@ -710,16 +799,58 @@
         <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>47</v>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -729,7 +860,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="24" customWidth="1"/>
@@ -738,106 +869,98 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="0" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="0" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="0" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="0" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="0" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="0" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="0" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="0" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="0" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="0" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="0" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="0" t="s">
-        <v>72</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>73</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
